--- a/Uploads/Data/COLL_REPRO_TEMPLATE.xlsx
+++ b/Uploads/Data/COLL_REPRO_TEMPLATE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Erica.Williams\Documents\GitHub\SQL-Database-Corrections\Uploads\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Erica.Levine\Documents\GitHub\SQL-Database-Corrections\Uploads\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A59E74AD-825D-437E-B98B-6A2266D179C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CBAD07A-C7F7-48E9-8191-1C3DAD651FBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2108D022-863A-4DDA-9361-349A7F55884E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{2108D022-863A-4DDA-9361-349A7F55884E}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="2" r:id="rId1"/>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5087" uniqueCount="627">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5111" uniqueCount="632">
   <si>
     <t>DataStatus</t>
   </si>
@@ -1941,6 +1941,21 @@
   </si>
   <si>
     <t>0=imm</t>
+  </si>
+  <si>
+    <t>TB Braden South</t>
+  </si>
+  <si>
+    <t>Erica Williams</t>
+  </si>
+  <si>
+    <t>Sex ratio project station</t>
+  </si>
+  <si>
+    <t>Added via SMSS for sex ratio project samples</t>
+  </si>
+  <si>
+    <t>TB Braden South 9</t>
   </si>
 </sst>
 </file>
@@ -2364,8 +2379,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{493C3DDF-B5B4-4E3C-8AD3-ADABB450E83E}" name="Table1" displayName="Table1" ref="A1:AF175" totalsRowShown="0" headerRowDxfId="33" dataDxfId="32">
-  <autoFilter ref="A1:AF175" xr:uid="{493C3DDF-B5B4-4E3C-8AD3-ADABB450E83E}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{493C3DDF-B5B4-4E3C-8AD3-ADABB450E83E}" name="Table1" displayName="Table1" ref="A1:AF176" totalsRowShown="0" headerRowDxfId="33" dataDxfId="32">
+  <autoFilter ref="A1:AF176" xr:uid="{493C3DDF-B5B4-4E3C-8AD3-ADABB450E83E}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P175">
     <sortCondition ref="A1:A175"/>
   </sortState>
@@ -6125,7 +6140,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9135BC8C-C095-4174-876F-A976B8C1179A}">
-  <dimension ref="A1:AF175"/>
+  <dimension ref="A1:AF176"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19" style="2" bestFit="1" customWidth="1"/>
@@ -23312,6 +23327,104 @@
         <v>9</v>
       </c>
     </row>
+    <row r="176" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A176" s="2">
+        <v>401</v>
+      </c>
+      <c r="B176" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C176" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D176" s="2" t="s">
+        <v>627</v>
+      </c>
+      <c r="E176" s="2">
+        <v>9</v>
+      </c>
+      <c r="F176" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G176" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H176" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I176" s="2">
+        <v>27.495699999999999</v>
+      </c>
+      <c r="J176" s="2">
+        <v>82.523679999999999</v>
+      </c>
+      <c r="K176" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="L176" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M176" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N176" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="O176" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P176" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q176" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="R176" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="S176" s="3">
+        <v>46113</v>
+      </c>
+      <c r="T176" s="3">
+        <v>73050</v>
+      </c>
+      <c r="U176" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="V176" s="7">
+        <v>46141</v>
+      </c>
+      <c r="W176" s="2" t="s">
+        <v>628</v>
+      </c>
+      <c r="X176" s="7">
+        <v>46141</v>
+      </c>
+      <c r="Y176" s="2" t="s">
+        <v>628</v>
+      </c>
+      <c r="Z176" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA176" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB176" s="2" t="s">
+        <v>629</v>
+      </c>
+      <c r="AC176" s="2" t="s">
+        <v>630</v>
+      </c>
+      <c r="AD176" s="2" t="s">
+        <v>631</v>
+      </c>
+      <c r="AE176" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AF176" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
